--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>667.3099999999999</v>
+        <v>670.76</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>814.8099999999999</v>
+        <v>813.67</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5659.15</v>
+        <v>5710.62</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7736.65</v>
+        <v>7807.02</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2611.51</v>
+        <v>2629.69</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11159.79</v>
+        <v>11091.98</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2579.86</v>
+        <v>2586.2</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>690.75</v>
+        <v>701.5700000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4115.14</v>
+        <v>4091.5</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2504.42</v>
+        <v>2438.47</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7819.96</v>
+        <v>7806.88</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1456.98</v>
+        <v>1454.55</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>216.29</v>
+        <v>218.96</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1336.57</v>
+        <v>1343.77</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2806.78</v>
+        <v>2821.89</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>456.04</v>
+        <v>458.5</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5494.74</v>
+        <v>5536.36</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17249.47</v>
+        <v>17314.82</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>42686.97</v>
+        <v>42880.84</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13832.53</v>
+        <v>14144.49</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1434.61</v>
+        <v>1439.05</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8771.440000000001</v>
+        <v>8854.76</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>562.3</v>
+        <v>563.59</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8335.32</v>
+        <v>8391.110000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6499.71</v>
+        <v>6543.21</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2700.71</v>
+        <v>2692.18</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>18790.08</v>
+        <v>18749.2</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>12782.37</v>
+        <v>12754.56</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5752.07</v>
+        <v>5739.55</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>61834.7</v>
+        <v>61710.74</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>319559.17</v>
+        <v>317709.5</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>25615.86</v>
+        <v>25467.59</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7064.56</v>
+        <v>7023.67</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>370.28</v>
+        <v>368.46</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7132.16</v>
+        <v>7097.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Coquimbo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>707418-208-CM25</t>
+          <t>527481-12-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SODIMAC S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.792.430-K</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>670.76</v>
+        <v>9782.370000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1079505-1321-CM25</t>
+          <t>2450-70-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>813.67</v>
+        <v>14104.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3884-22-CM26</t>
+          <t>1079505-67-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5710.62</v>
+        <v>3945.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>527481-12-CM26</t>
+          <t>1346282-75-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>RASTRO RETAIL SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.888.564-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7807.02</v>
+        <v>604.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1346282-54-CM26</t>
+          <t>1346282-74-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIALIZADORA R&amp;D MODULARES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.312.472-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2629.69</v>
+        <v>1133.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3712-86-CM26</t>
+          <t>3712-217-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FIRAMCO SPA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.942.697-1</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>11091.98</v>
+        <v>7148.07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1159-40-CM26</t>
+          <t>1346282-98-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2586.2</v>
+        <v>555.35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3712-103-CM26</t>
+          <t>2708-246-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.040.700-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>MUNICIPALIDAD DE OVALLE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIALIZADORA EXPRESSVIRTUAL SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.511.768-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>701.5700000000001</v>
+        <v>1126.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1079505-105-CM26</t>
+          <t>1079505-286-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.566.610-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4091.5</v>
+        <v>21547.06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2450-381-CM26</t>
+          <t>3712-409-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2438.47</v>
+        <v>3530.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2450-424-CM26</t>
+          <t>3712-342-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>RASTRO RETAIL SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.888.564-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>7806.88</v>
+        <v>1020.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2450-440-CM26</t>
+          <t>3712-441-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>COMERCIAL ANDES SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.765.995-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1454.55</v>
+        <v>3082.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3267-53-CM26</t>
+          <t>3712-547-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.041.000-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>218.96</v>
+        <v>5744.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3712-310-CM26</t>
+          <t>527481-85-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1343.77</v>
+        <v>11228.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3712-311-CM26</t>
+          <t>3712-669-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2821.89</v>
+        <v>3511.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3712-312-CM26</t>
+          <t>1346282-354-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>458.5</v>
+        <v>879.8200000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>627786-91-CM26</t>
+          <t>3712-819-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5536.36</v>
+        <v>666.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2450-517-CM26</t>
+          <t>527481-104-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17314.82</v>
+        <v>7541.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>527481-60-CM26</t>
+          <t>1079505-1011-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA expressVirtual SpA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.511.768-2</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>42880.84</v>
+        <v>1694.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>527481-61-CM26</t>
+          <t>707418-208-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>14144.49</v>
+        <v>670.76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1159-148-CM26</t>
+          <t>1079505-1321-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1439.05</v>
+        <v>813.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1079505-354-CM26</t>
+          <t>3884-22-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.505.206-1</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8854.76</v>
+        <v>5710.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3712-491-CM26</t>
+          <t>527481-12-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>563.59</v>
+        <v>7807.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3712-499-CM26</t>
+          <t>1346282-54-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.041.500-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8391.110000000001</v>
+        <v>2629.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3712-501-CM26</t>
+          <t>3712-86-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL EL TORO SPA</t>
+          <t>FIRAMCO SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.209.677-3</t>
+          <t>77.942.697-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6543.21</v>
+        <v>11091.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1657-347-CM26</t>
+          <t>1159-40-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2692.18</v>
+        <v>2586.2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3512-677-CM26</t>
+          <t>3712-103-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Comercializadora TJB S.A.</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.095.313-k</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>18749.2</v>
+        <v>701.5700000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3512-675-CM26</t>
+          <t>1079505-105-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>60.505.206-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>12754.56</v>
+        <v>4091.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3512-676-CM26</t>
+          <t>2450-381-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5739.55</v>
+        <v>2438.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2446-825-CM26</t>
+          <t>2450-424-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>61710.74</v>
+        <v>7806.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2446-830-CM26</t>
+          <t>2450-440-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.040.100-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>317709.5</v>
+        <v>1454.55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3512-683-CM26</t>
+          <t>3267-53-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.000-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE RIO HURTADO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>25467.59</v>
+        <v>218.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3512-684-CM26</t>
+          <t>3712-310-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7023.67</v>
+        <v>1343.77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2125-1495-CM26</t>
+          <t>3712-311-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.407-k</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Hales Hnos y Cia Ltda</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>83.535.000-2</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>368.46</v>
+        <v>2821.89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3512-699-CM26</t>
+          <t>3712-312-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.041.500-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,6 +2643,1165 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
+        <v>458.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>627786-91-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>5536.36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2450-517-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>17314.82</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>527481-60-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA expressVirtual SpA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.511.768-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>42880.84</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>527481-61-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>69.041.100-8</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>14144.49</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1159-148-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.308.000-7</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1439.05</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1079505-354-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IV ZONA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>8854.76</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3712-491-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>563.59</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3712-499-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>COMERCIAL EL TORO SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.209.677-3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>8391.110000000001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3712-501-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>COMERCIAL EL TORO SPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.209.677-3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>6543.21</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1657-347-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>2692.18</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3512-675-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>12754.56</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3512-676-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>5739.55</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3512-677-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Comercializadora TJB S.A.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.095.313-k</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>18749.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2446-825-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>61710.74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2446-830-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>317709.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3512-683-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>25467.59</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3512-684-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>7023.67</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2125-1495-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.606.407-k</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DR. HUMBERTO ELORZA CORTES</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>368.46</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3512-699-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.041.200-4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
         <v>7097.1</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3712-409-CM25</t>
+          <t>3712-342-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>RASTRO RETAIL SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.888.564-6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3530.89</v>
+        <v>1020.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3712-342-CM25</t>
+          <t>3712-409-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>RASTRO RETAIL SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.888.564-6</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1020.42</v>
+        <v>3530.89</v>
       </c>
     </row>
     <row r="13">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA expressVirtual SpA</t>
+          <t>COMERCIALIZADORA EXPRESSVIRTUAL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3803,6 +3803,67 @@
       </c>
       <c r="M55" s="2" t="n">
         <v>7097.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3712-594-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>2649.66</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
@@ -562,7 +562,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.312.472-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>77.888.564-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>77.765.995-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>77.801.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1517,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1582,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1647,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1895,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1960,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2025,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2090,11 @@
           <t>77.942.697-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2155,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2220,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2411,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2476,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2541,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2606,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2736,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2801,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2866,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2992,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3057,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3183,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3797,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3923,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1083,7 +1083,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3712-342-CM25</t>
+          <t>3712-409-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>RASTRO RETAIL SPA</t>
+          <t>FIMCO SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.888.564-6</t>
+          <t>77.801.815-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1020.42</v>
+        <v>3530.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3712-409-CM25</t>
+          <t>3712-342-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>FIMCO SPA</t>
+          <t>RASTRO RETAIL SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.801.815-2</t>
+          <t>77.888.564-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3530.89</v>
+        <v>1020.42</v>
       </c>
     </row>
     <row r="13">
@@ -1847,7 +1847,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3884-22-CM26</t>
+          <t>527481-12-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.041.100-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>5710.62</v>
+        <v>7807.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>527481-12-CM26</t>
+          <t>3884-22-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.041.100-8</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ILUSTRE MINICIPALIDAD DE COMBARBALA</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7807.02</v>
+        <v>5710.62</v>
       </c>
     </row>
     <row r="25">
@@ -3627,7 +3627,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2446-830-CM26</t>
+          <t>3512-683-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>69.041.200-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3682,13 +3682,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>317709.5</v>
+        <v>25467.59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3512-683-CM26</t>
+          <t>2446-830-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3708,17 +3708,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.041.200-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ILLAPEL</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>25467.59</v>
+        <v>317709.5</v>
       </c>
     </row>
     <row r="53">
@@ -3996,6 +3996,132 @@
       </c>
       <c r="M56" s="2" t="n">
         <v>2649.66</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3712-690-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.041.500-3</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS VILOS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>712.55</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>627786-172-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>60.505.206-1</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>4834.83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/coquimbo.xlsx
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
